--- a/output/finalVersion/表4_比較法調查估價表_已填.xlsx
+++ b/output/finalVersion/表4_比較法調查估價表_已填.xlsx
@@ -4905,7 +4905,7 @@
       <c r="H8" s="139" t="n"/>
       <c r="I8" s="140" t="n"/>
       <c r="J8" s="228" t="n">
-        <v>-0.2375</v>
+        <v>0.2375</v>
       </c>
       <c r="K8" s="227" t="inlineStr">
         <is>
@@ -4915,7 +4915,7 @@
       <c r="L8" s="139" t="n"/>
       <c r="M8" s="140" t="n"/>
       <c r="N8" s="228" t="n">
-        <v>-0.1375</v>
+        <v>0.1375</v>
       </c>
       <c r="O8" s="227" t="inlineStr">
         <is>
@@ -4925,7 +4925,7 @@
       <c r="P8" s="139" t="n"/>
       <c r="Q8" s="140" t="n"/>
       <c r="R8" s="228" t="n">
-        <v>-0.1775</v>
+        <v>0.1775</v>
       </c>
       <c r="S8" s="211" t="n"/>
     </row>
